--- a/templates/testfaelle_pacs008_minimal.xlsx
+++ b/templates/testfaelle_pacs008_minimal.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,116 +425,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:AV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="15" customWidth="1" min="30" max="30"/>
+    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="46" max="46"/>
+    <col width="23" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestcaseID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Titel</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ziel</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Erwartetes Ergebnis</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Flavor</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>BAH From BIC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>BAH To BIC</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>InstgAgt BIC</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>InstdAgt BIC</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Debtor Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Strasse</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Hausnummer</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor PLZ</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Ort</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Land</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Debtor IBAN</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Kontonummer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Debtor Kontoschema</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DbtrAgt BIC</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>DbtrAgt ClrSysMmbId</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>IntrmyAgt1 BIC</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>IntrmyAgt1 ClrSysMmbId</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>IntrmyAgt2 BIC</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>IntrmyAgt3 BIC</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Creditor Name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Strasse</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Hausnummer</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor PLZ</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Ort</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Land</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Creditor IBAN</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Kontonummer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Creditor Kontoschema</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>CdtrAgt BIC</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>CdtrAgt ClrSysMmbId</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>IntrBkSttlmAmt</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Währung</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>IntrBkSttlmDt</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>SttlmMtd</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>ChrgBr</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>UETR</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>PurposeCode</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>CategoryPurpose</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Verwendungszweck</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>ViolateRule</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Weitere Testdaten</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Erwartete API-Antwort</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Bemerkungen</t>
         </is>
@@ -531,17 +723,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-PACS-SCAFFOLD-001</t>
+          <t>TC-PACS-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scaffold Smoke</t>
+          <t>Minimal CBPR+</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minimal pacs.008 smoke row</t>
+          <t>Minimale CBPR+ pacs.008</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -581,52 +773,461 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Bahnhofstrasse</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>CH5604835012345678009</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>UBSWCHZH80A</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Empfaenger GmbH</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Unter den Linden</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10117</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>DE89370400440532013000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>DEUTDEFFXXX</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>INDA</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>WP-01 scaffold stub</t>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Rechnung 2026-0001</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Minimal smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC-PACS-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Intermediary Agent</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CBPR+ mit einem Intermediary</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CBPR+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Muster AG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bahnhofstrasse</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CH5604835012345678009</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>US Partner Inc</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Wall Street</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>042000021</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>BBAN</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>TRAD</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Trade settlement</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Cross-border mit Intermediary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC-PACS-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ClrSysMmbId</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fedwire ClrSysMmbId statt BIC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CBPR+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FRNYUS33</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FRNYUS33</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Muster AG</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bahnhofstrasse</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CH5604835012345678009</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>NY Corp</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Fifth Avenue</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10010</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>BBAN</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>021000021</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Direct Fedwire</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>IntrmyAgt1.FinInstnId.BICFI=CHASUS33XXX; ChrgsInf[0].Amt=15.00; ChrgsInf[0].Ccy=USD</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>Test ClrSysMmbId + overrides</t>
         </is>
       </c>
     </row>
